--- a/hardware/SPI NAND Flash Breakout Board/8 GBit/v0.1.0/spi_nand_bom.xlsx
+++ b/hardware/SPI NAND Flash Breakout Board/8 GBit/v0.1.0/spi_nand_bom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/dstjohn_email_sc_edu/Documents/Desktop/Edge-Computing-Power-Management-Development-Kit/hardware/SPI NAND Flash Breakout Board/8 GBit/v0.1.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidstjohn/Desktop/Edge-Computing-Power-Management-Development-Kit/hardware/SPI NAND Flash Breakout Board/8 GBit/v0.1.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="97" documentId="11_5A4B2C90D3AEA2794F446FDFF5D8B87F547F059E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7011B3E0-24B8-4C40-B0AA-E9A767C77FCB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="3" r:id="rId1"/>
@@ -300,10 +300,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,18 +452,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A2B87F-5173-4193-A830-E49BA38F1355}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="7.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
